--- a/Sistem za podrsku pri tehnickom pregledu/kjar/src/main/resources/rules/templateable/template-inspection-issue.xlsx
+++ b/Sistem za podrsku pri tehnickom pregledu/kjar/src/main/resources/rules/templateable/template-inspection-issue.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="104">
   <si>
     <t>system</t>
   </si>
@@ -291,6 +291,39 @@
   </si>
   <si>
     <t>REFLECTIVE_VEST_MISSING</t>
+  </si>
+  <si>
+    <t>WHEEL_TIRE</t>
+  </si>
+  <si>
+    <t>WHEEL_MAPPING</t>
+  </si>
+  <si>
+    <t>WHEEL_TIRE_INVALID</t>
+  </si>
+  <si>
+    <t>BRAKE_TEST</t>
+  </si>
+  <si>
+    <t>BRAKE_FORCE</t>
+  </si>
+  <si>
+    <t>LOW_FORCE</t>
+  </si>
+  <si>
+    <t>BRAKE_IMBALANCE</t>
+  </si>
+  <si>
+    <t>LOW_BRAKE_IMBALANCE_FRONT</t>
+  </si>
+  <si>
+    <t>LOW_BRAKE_IMBALANCE_REAR</t>
+  </si>
+  <si>
+    <t>DISK_OVALITY</t>
+  </si>
+  <si>
+    <t>LOW_OVALITY</t>
   </si>
 </sst>
 </file>
@@ -1230,6 +1263,61 @@
         <v>92</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
